--- a/ResourcesPK/pjpHeaderBulkCreationExcel.xlsx
+++ b/ResourcesPK/pjpHeaderBulkCreationExcel.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="88">
   <si>
     <t>Distributor*</t>
   </si>
@@ -265,6 +265,24 @@
   </si>
   <si>
     <t>PJP_DESC7D458</t>
+  </si>
+  <si>
+    <t>DSR_810F1</t>
+  </si>
+  <si>
+    <t>PJP5206F</t>
+  </si>
+  <si>
+    <t>PJP_DESCEB41D</t>
+  </si>
+  <si>
+    <t>DSR_20AFD</t>
+  </si>
+  <si>
+    <t>PJP60A61</t>
+  </si>
+  <si>
+    <t>PJP_DESCC4B7D</t>
   </si>
 </sst>
 </file>
@@ -630,13 +648,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
